--- a/РАБОЧИЙ СТОЛ/ПРОБЛЕМЫ/ПОКОМ/ПОКОМ дозаказ недогрузов.xlsx
+++ b/РАБОЧИЙ СТОЛ/ПРОБЛЕМЫ/ПОКОМ/ПОКОМ дозаказ недогрузов.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\ПРОБЛЕМЫ\ПОКОМ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC773AAD-3E83-475E-9A62-D3A009FB265E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2628269-AF3C-4E5F-9FA0-D2AC4EC3CDE8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,17 +16,23 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="66">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -197,6 +203,33 @@
   </si>
   <si>
     <t>кооф</t>
+  </si>
+  <si>
+    <t>P004844</t>
+  </si>
+  <si>
+    <t>P003265</t>
+  </si>
+  <si>
+    <t>КОД</t>
+  </si>
+  <si>
+    <t>P003986</t>
+  </si>
+  <si>
+    <t>P003988</t>
+  </si>
+  <si>
+    <t>P002555</t>
+  </si>
+  <si>
+    <t>P003957</t>
+  </si>
+  <si>
+    <t>P003260</t>
+  </si>
+  <si>
+    <t>P004178</t>
   </si>
 </sst>
 </file>
@@ -243,7 +276,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -272,8 +305,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -296,12 +335,271 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -314,15 +612,53 @@
     <xf numFmtId="164" fontId="1" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{6649B6CD-6934-4403-9162-6E1B4A67F778}"/>
@@ -5162,310 +5498,340 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115C5090-3937-4180-99A7-EED19F737F60}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="94.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.140625" style="11" customWidth="1"/>
-    <col min="3" max="7" width="7.5703125" style="10" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" style="11" customWidth="1"/>
+    <col min="4" max="8" width="7.5703125" style="10" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="D1" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="28"/>
+      <c r="F1" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="28"/>
+      <c r="H1" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="10" t="s">
+      <c r="I1" s="28"/>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="33"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="I2" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="39">
         <v>1</v>
       </c>
-      <c r="C3" s="10">
+      <c r="D3" s="30">
         <v>400</v>
       </c>
-      <c r="D3" s="10">
-        <f>C3*B3</f>
+      <c r="E3" s="20">
+        <f>D3*C3</f>
         <v>400</v>
       </c>
-      <c r="E3" s="10">
+      <c r="F3" s="19">
         <v>100</v>
       </c>
-      <c r="F3" s="10">
-        <f>E3*B3</f>
+      <c r="G3" s="20">
+        <f>F3*C3</f>
         <v>100</v>
       </c>
-      <c r="G3" s="10">
+      <c r="H3" s="19">
         <v>1650</v>
       </c>
-      <c r="H3">
-        <f>G3*B3</f>
+      <c r="I3" s="13">
+        <f>H3*C3</f>
         <v>1650</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="40">
         <v>1</v>
       </c>
-      <c r="C4" s="10">
+      <c r="D4" s="31">
         <v>400</v>
       </c>
-      <c r="D4" s="10">
-        <f t="shared" ref="D4:D10" si="0">C4*B4</f>
+      <c r="E4" s="22">
+        <f t="shared" ref="E4:E10" si="0">D4*C4</f>
         <v>400</v>
       </c>
-      <c r="E4" s="10">
+      <c r="F4" s="21">
         <v>950</v>
       </c>
-      <c r="F4" s="10">
-        <f t="shared" ref="F4:F10" si="1">E4*B4</f>
+      <c r="G4" s="22">
+        <f t="shared" ref="G4:G10" si="1">F4*C4</f>
         <v>950</v>
       </c>
-      <c r="G4" s="10">
+      <c r="H4" s="21">
         <v>1550</v>
       </c>
-      <c r="H4">
-        <f t="shared" ref="H4:H10" si="2">G4*B4</f>
+      <c r="I4" s="15">
+        <f t="shared" ref="I4:I10" si="2">H4*C4</f>
         <v>1550</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="40">
         <v>1</v>
       </c>
-      <c r="C5" s="10">
+      <c r="D5" s="31">
         <v>3100</v>
       </c>
-      <c r="D5" s="10">
+      <c r="E5" s="22">
         <f t="shared" si="0"/>
         <v>3100</v>
       </c>
-      <c r="E5" s="10">
+      <c r="F5" s="21">
         <v>2450</v>
       </c>
-      <c r="F5" s="10">
+      <c r="G5" s="22">
         <f t="shared" si="1"/>
         <v>2450</v>
       </c>
-      <c r="G5" s="10">
+      <c r="H5" s="21">
         <v>5000</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="15">
         <f t="shared" si="2"/>
         <v>5000</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="40">
         <v>1</v>
       </c>
-      <c r="C6" s="10">
+      <c r="D6" s="31">
         <v>1200</v>
       </c>
-      <c r="D6" s="10">
+      <c r="E6" s="22">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="E6" s="10">
+      <c r="F6" s="21">
         <v>1000</v>
       </c>
-      <c r="F6" s="10">
+      <c r="G6" s="22">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="G6" s="10">
+      <c r="H6" s="21">
         <v>3600</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="15">
         <f t="shared" si="2"/>
         <v>3600</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="40">
         <v>0.4</v>
       </c>
-      <c r="C7" s="10">
+      <c r="D7" s="31">
         <v>2300</v>
       </c>
-      <c r="D7" s="10">
+      <c r="E7" s="22">
         <f t="shared" si="0"/>
         <v>920</v>
       </c>
-      <c r="E7" s="10">
+      <c r="F7" s="21">
         <v>1550</v>
       </c>
-      <c r="F7" s="10">
+      <c r="G7" s="22">
         <f t="shared" si="1"/>
         <v>620</v>
       </c>
-      <c r="G7" s="10">
+      <c r="H7" s="21">
         <v>6100</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="15">
         <f t="shared" si="2"/>
         <v>2440</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="40">
         <v>0.35</v>
       </c>
-      <c r="C8" s="10">
+      <c r="D8" s="31">
         <v>350</v>
       </c>
-      <c r="D8" s="10">
+      <c r="E8" s="22">
         <f t="shared" si="0"/>
         <v>122.49999999999999</v>
       </c>
-      <c r="E8" s="10">
+      <c r="F8" s="21">
         <v>500</v>
       </c>
-      <c r="F8" s="10">
+      <c r="G8" s="22">
         <f t="shared" si="1"/>
         <v>175</v>
       </c>
-      <c r="G8" s="10">
+      <c r="H8" s="21">
         <v>2200</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="15">
         <f t="shared" si="2"/>
         <v>770</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="40">
         <v>0.4</v>
       </c>
-      <c r="C9" s="10">
+      <c r="D9" s="31">
         <v>400</v>
       </c>
-      <c r="D9" s="10">
+      <c r="E9" s="22">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
-      <c r="E9" s="10">
+      <c r="F9" s="21">
         <v>360</v>
       </c>
-      <c r="F9" s="10">
+      <c r="G9" s="22">
         <f t="shared" si="1"/>
         <v>144</v>
       </c>
-      <c r="G9" s="10">
+      <c r="H9" s="21">
         <v>850</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="15">
         <f t="shared" si="2"/>
         <v>340</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="42">
         <v>0.4</v>
       </c>
-      <c r="C10" s="10">
+      <c r="D10" s="32">
         <v>450</v>
       </c>
-      <c r="D10" s="10">
+      <c r="E10" s="24">
         <f t="shared" si="0"/>
         <v>180</v>
       </c>
-      <c r="E10" s="10">
+      <c r="F10" s="23">
         <v>400</v>
       </c>
-      <c r="F10" s="10">
+      <c r="G10" s="24">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="G10" s="10">
+      <c r="H10" s="23">
         <v>850</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="17">
         <f t="shared" si="2"/>
         <v>340</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D11" s="10">
-        <f>SUM(D3:D10)</f>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E11" s="10">
+        <f>SUM(E3:E10)</f>
         <v>6482.5</v>
       </c>
-      <c r="F11" s="10">
-        <f>SUM(F3:F10)</f>
+      <c r="G11" s="10">
+        <f>SUM(G3:G10)</f>
         <v>5599</v>
       </c>
-      <c r="H11" s="10">
-        <f>SUM(H3:H10)</f>
+      <c r="I11" s="10">
+        <f>SUM(I3:I10)</f>
         <v>15690</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
